--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260831.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>197,661,000</t>
+          <t>99,498,442</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,498,442</t>
+          <t>197,661,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1319,17 +1319,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>B95552</t>
+          <t>B95553</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1A</t>
+          <t>P08凱控1B</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>85,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
@@ -1337,17 +1337,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>B95553</t>
+          <t>B95555</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>P08凱控1B</t>
+          <t>P09凱控1B</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>185,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
@@ -1355,17 +1355,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>B95555</t>
+          <t>B96525</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>P09凱控1B</t>
+          <t>P11元金2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>120,000,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr"/>
@@ -1373,17 +1373,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>B96525</t>
+          <t>B97872</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>P11元金2</t>
+          <t>P13富邦金1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>120,000,000</t>
+          <t>45,000,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
@@ -1391,17 +1391,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>B97872</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>P13富邦金1</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>45,000,000</t>
+          <t>31,086,695,777</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr"/>
@@ -1409,17 +1409,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>31,086,695,777</t>
+          <t>5,110,933,426</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
@@ -1427,38 +1427,20 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5,110,933,426</t>
+          <t>-49,471,279</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>PFUR_NTD</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>-49,471,279</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
